--- a/output/2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx
+++ b/output/2026-10-03_01_Malesia_Pahang_ATEX_Equipment_Services.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore/stockist dal 2004 di illuminazione e componenti elettrici per aree pericolose (Oil&amp;Gas, chimico, marine, mining), certificati IEC/CENELEC/CSA/UL/FM/ATEX/IECEx. HQ fuori Pahang ma copre il mercato malese incluso Pahang.</t>
+          <t>Distributore/stockist dal 2004 di illuminazione e componenti elettrici per aree pericolose (Oil&amp;Gas, chimico, marine, mining), certificati IEC/CENELEC/CSA/UL/FM/ATEX/IECEx. HQ fuori Pahang ma copre il mercato malese incluso Pahang. [DUPLICATO — vedi anche: 2026-10-01_03_Malesia_Kedah_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -558,7 +558,6 @@
           <t>See Kwong Electric (KL) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Selangor (Puchong) - distributore nazionale, nessuna sede in Pahang</t>
@@ -569,11 +568,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore di prodotti per aree pericolose (cable glands, fusibili industriali, illuminazione explosion-proof certificata ATEX) per oil&amp;gas e manifatturiero, attivo dal 1982. Sito web, telefono ed email non reperiti da fonte verificabile.</t>
+          <t>Distributore di prodotti per aree pericolose (cable glands, fusibili industriali, illuminazione explosion-proof certificata ATEX) per oil&amp;gas e manifatturiero, attivo dal 1982. Sito web, telefono ed email non reperiti da fonte verificabile. [DUPLICATO — vedi anche: 2026-10-02_03_Malesia_Melaka_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -615,7 +612,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Stockist/value-add manufacturer di prodotti explosion-proof &amp; elettrici, strumentazione; channel partner di marchi come CEAG/Rittal/Mennekes. HQ fuori Pahang ma copre il mercato malese incluso zone limitrofe.</t>
+          <t>Stockist/value-add manufacturer di prodotti explosion-proof &amp; elettrici, strumentazione; channel partner di marchi come CEAG/Rittal/Mennekes. HQ fuori Pahang ma copre il mercato malese incluso zone limitrofe. [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
